--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Programático</t>
@@ -137,7 +137,19 @@
     <t>Cuenta pública</t>
   </si>
   <si>
-    <t>Dirección Académica, Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a lo programático, que forma parte de la cuenta pública.</t>
+  </si>
+  <si>
+    <t>Contable</t>
+  </si>
+  <si>
+    <t>Estados financieros</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
   </si>
   <si>
     <t>Presupuestal</t>
@@ -146,49 +158,37 @@
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>Contable</t>
-  </si>
-  <si>
-    <t>Estados financieros</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>76F4953FA4A9D02A1B9FDABEAF7B6A49</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/2do_Trimestre/Informacion%20Programatica/informacion%20Programatica.pdf</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>La Secretaría de Planeación y Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a lo programático, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
-    <t>41F46556BCFCE149F28505A9F90B743D</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/2do_Trimestre/Informacion%20Preupuestal/Informacion%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>La Secretaría de Planeación y Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
-    <t>90B2ED8A0B08EDF0C215B246B86C559E</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/2do_Trimestre/Informacion%20Contable/informacion%20Contable.pdf</t>
-  </si>
-  <si>
-    <t>La Secretaría de Planeación y Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
+  </si>
+  <si>
+    <t>EDACE9265CD82445E4FF2A6805EE0C07</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Contable/Informaci%c3%b3n%20Contable.pdf</t>
+  </si>
+  <si>
+    <t>20/07/2023</t>
+  </si>
+  <si>
+    <t>35538918972DB88B8BD59C35FFC340FB</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Presupuestal/Informaci%c3%b3n%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>7B80B6D42E29AA0C6DC2A909935347D8</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Program%c3%a1tica/Informaci%c3%b3n%20Program%c3%a1tica.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
   </si>
 </sst>
 </file>
@@ -584,17 +584,17 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="171.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="195" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="93.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="229" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="217.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -757,78 +757,78 @@
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -839,16 +839,16 @@
         <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>55</v>
@@ -857,16 +857,16 @@
         <v>55</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +880,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E192">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -895,12 +895,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
